--- a/favorites.xlsx
+++ b/favorites.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效率小技巧" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="热门开源仓库" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="技术冷知识" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="程序员梗" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="更新日志" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,11 +60,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +510,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>find 的 Rust 替代品，秒级模糊查找文件</t>
+          <t>find的Rust替代品，秒级模糊查找文件</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -517,7 +520,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fd /config.*ts/</t>
+          <t>fd "config.*ts"</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,7 +557,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>grep 的极速替代品，代码搜索利器</t>
+          <t>grep的极速替代品，代码搜索利器</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -564,7 +567,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>rg /TODO/ --type js</t>
+          <t>rg "TODO" --type js</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -594,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -667,7 +670,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>从AI玩具进化成实用开发工具，能帮你在重构时少踩坑</t>
+          <t>从AI玩具进化成实用开发工具</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -766,6 +769,44 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>repo-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Odysseus</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>自托管AI工作台，统一管理所有AI订阅和本地大模型</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>YouTube顶流PewDiePie随手搓出来的工具，4天狂揽5万多GitHub Star</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ai,self-hosted,llm,pewdiepie</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>viral</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
@@ -782,20 +823,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>添加日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>trivia-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>世界上第一个bug真的是只虫子</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1947年9月，Grace Hopper在Harvard Mark II计算机的继电器触点里发现了一只烤焦的飞蛾，她把飞蛾尸体贴在工作日志上，写着：First actual case of bug being found.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>history,bug,grace-hopper</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>添加日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>meme-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>My code doesn't work, I don't know why. My code works, I don't know why.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>programmer,debugging</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>新增内容</t>
         </is>
@@ -809,7 +989,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>初始创建：fd、ripgrep技巧 + OpenDevin-Next、LocalLLM-Runtime、Hono-X仓库</t>
+          <t>初始创建</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>追加：Odysseus + 第一个bug冷知识 + 程序员梗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>新增：消费品牌AI工具调研</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>新增：2026年AI/半导体/芯片/股市新闻汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>新增：2026年顶会论文汇总（CVPR/ICLR/ICML/ACL/MLSys）</t>
         </is>
       </c>
     </row>

--- a/favorites.xlsx
+++ b/favorites.xlsx
@@ -89,25 +89,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -115,7 +112,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -127,13 +124,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00C0C0C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00CD7F32"/>
         </patternFill>
       </fill>
     </dxf>
@@ -237,7 +227,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!C21</f>
+              <f>'消费品牌AI'!B21</f>
             </strRef>
           </tx>
           <spPr>
@@ -261,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
+              <f>'消费品牌AI'!$B$21:$F$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$C$22:$C$26</f>
+              <f>'消费品牌AI'!$B$22:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -275,7 +265,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!D21</f>
+              <f>'消费品牌AI'!C21</f>
             </strRef>
           </tx>
           <spPr>
@@ -299,12 +289,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
+              <f>'消费品牌AI'!$B$21:$F$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$D$22:$D$26</f>
+              <f>'消费品牌AI'!$C$22:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -313,7 +303,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!E21</f>
+              <f>'消费品牌AI'!D21</f>
             </strRef>
           </tx>
           <spPr>
@@ -337,12 +327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
+              <f>'消费品牌AI'!$B$21:$F$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$E$22:$E$26</f>
+              <f>'消费品牌AI'!$D$22:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -351,7 +341,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!F21</f>
+              <f>'消费品牌AI'!E21</f>
             </strRef>
           </tx>
           <spPr>
@@ -375,12 +365,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
+              <f>'消费品牌AI'!$B$21:$F$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$F$22:$F$26</f>
+              <f>'消费品牌AI'!$E$22:$E$36</f>
             </numRef>
           </val>
         </ser>
@@ -389,7 +379,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!G21</f>
+              <f>'消费品牌AI'!F21</f>
             </strRef>
           </tx>
           <spPr>
@@ -413,392 +403,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
+              <f>'消费品牌AI'!$B$21:$F$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$G$22:$G$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!H21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1ABC9C"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="1ABC9C"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$H$22:$H$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!I21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="F1C40F"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="F1C40F"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$I$22:$I$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!J21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="E91E63"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="E91E63"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$J$22:$J$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!K21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="00BCD4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="00BCD4"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$K$22:$K$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!L21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FF5722"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="FF5722"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$L$22:$L$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="10"/>
-          <order val="10"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!M21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="795548"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="795548"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$M$22:$M$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="11"/>
-          <order val="11"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!N21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="607D8B"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="607D8B"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$N$22:$N$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="12"/>
-          <order val="12"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!O21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="8BC34A"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="8BC34A"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$O$22:$O$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="13"/>
-          <order val="13"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!P21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="FFC107"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="FFC107"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$P$22:$P$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="14"/>
-          <order val="14"/>
-          <tx>
-            <strRef>
-              <f>'消费品牌AI'!Q21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="03A9F4"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="03A9F4"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'消费品牌AI'!$B$22:$B$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'消费品牌AI'!$Q$22:$Q$26</f>
+              <f>'消费品牌AI'!$F$22:$F$36</f>
             </numRef>
           </val>
         </ser>
@@ -931,6 +541,21 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>美元/1M tokens</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1206,9 +831,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>9</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5760000"/>
@@ -1233,12 +858,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>11</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="5040000"/>
+    <ext cx="8640000" cy="5760000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1260,9 +885,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>10</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="5760000"/>
@@ -1287,12 +912,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>12</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="5040000"/>
+    <ext cx="8640000" cy="5760000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1601,10 +1226,6 @@
   </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1679,7 +1300,7 @@
           <t>Tips</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1689,8 +1310,8 @@
           <t>Repos</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>16</v>
+      <c r="B10" s="4" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -1699,7 +1320,7 @@
           <t>Consumer AI</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="4" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1709,7 +1330,7 @@
           <t>AI Models</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1719,8 +1340,8 @@
           <t>Tech News</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>53</v>
+      <c r="B13" s="4" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -1729,8 +1350,8 @@
           <t>Stock Market</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>24</v>
+      <c r="B14" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -1739,17 +1360,17 @@
           <t>Papers</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>27</v>
+      <c r="B15" s="4" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>总计</t>
         </is>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <f>SUM(B9:B15)</f>
         <v/>
       </c>
@@ -1768,18 +1389,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1789,42 +1400,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>品牌</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>工具</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>AI深度</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>用户体验</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>部署规模</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>技术壁垒</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>商业化</t>
         </is>
@@ -1846,19 +1457,19 @@
           <t>AI点单</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F4" s="5" t="n">
+      <c r="E4" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1878,19 +1489,19 @@
           <t>门店自动化</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1910,19 +1521,19 @@
           <t>食品安全AI</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="5" t="n">
+      <c r="D6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1942,19 +1553,19 @@
           <t>AI底层技术</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1974,19 +1585,19 @@
           <t>员工辅助AI</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="5" t="n">
+      <c r="E8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2006,19 +1617,19 @@
           <t>个性化推荐</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="5" t="n">
+      <c r="G9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2038,19 +1649,19 @@
           <t>需求预测AI（失败案例）</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2070,19 +1681,19 @@
           <t>智慧运营</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="5" t="n">
+      <c r="D11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2102,19 +1713,19 @@
           <t>AI语音点餐</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="D12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2134,19 +1745,19 @@
           <t>员工数字化</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2166,19 +1777,19 @@
           <t>AI巡检</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="5" t="n">
+      <c r="D14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="G14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2198,19 +1809,19 @@
           <t>AI巡检+品控</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F15" s="5" t="n">
+      <c r="E15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2230,19 +1841,19 @@
           <t>智能标准化</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2262,19 +1873,19 @@
           <t>AI Agent消费入口</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" s="5" t="n">
+      <c r="G17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2294,388 +1905,408 @@
           <t>AI数据平台</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>平均分</t>
         </is>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <f>AVERAGE(D4:D18)</f>
         <v/>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <f>AVERAGE(E4:E18)</f>
         <v/>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <f>AVERAGE(F4:F18)</f>
         <v/>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <f>AVERAGE(G4:G18)</f>
         <v/>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <f>AVERAGE(H4:H18)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="8" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>维度</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AI深度</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>用户体验</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>部署规模</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>技术壁垒</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>商业化</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>瑞幸咖啡</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="B22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>喜茶</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>奈雪的茶</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>蜜雪冰城</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>星巴克</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>星巴克</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>星巴克</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>库迪咖啡</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>肯德基</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>麦当劳</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t>海底捞</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t>茶百道</t>
-        </is>
-      </c>
-      <c r="O21" s="8" t="inlineStr">
-        <is>
-          <t>霸王茶姬</t>
-        </is>
-      </c>
-      <c r="P21" s="8" t="inlineStr">
-        <is>
-          <t>阿里通义千问</t>
-        </is>
-      </c>
-      <c r="Q21" s="8" t="inlineStr">
-        <is>
-          <t>蜜雪冰城</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>AI深度</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
         <v>8</v>
-      </c>
-      <c r="D22" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" t="n">
-        <v>8</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>7</v>
-      </c>
-      <c r="N22" t="n">
-        <v>6</v>
-      </c>
-      <c r="O22" t="n">
-        <v>6</v>
-      </c>
-      <c r="P22" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>用户体验</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>7</v>
       </c>
       <c r="D23" t="n">
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>奈雪的茶</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>蜜雪冰城</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>5</v>
       </c>
-      <c r="G23" t="n">
-        <v>7</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>星巴克</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>星巴克</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
         <v>9</v>
       </c>
-      <c r="I23" t="n">
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>星巴克</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="n">
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>库迪咖啡</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="n">
         <v>6</v>
       </c>
-      <c r="K23" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" t="n">
-        <v>7</v>
-      </c>
-      <c r="M23" t="n">
-        <v>7</v>
-      </c>
-      <c r="N23" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="D29" t="n">
         <v>9</v>
       </c>
-      <c r="P23" t="n">
+      <c r="E29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>肯德基</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" t="n">
         <v>8</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>麦当劳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>海底捞</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>茶百道</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>霸王茶姬</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>阿里通义千问</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>蜜雪冰城</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>部署规模</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>9</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="D36" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>7</v>
-      </c>
-      <c r="F24" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" t="n">
-        <v>7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>10</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>8</v>
-      </c>
-      <c r="M24" t="n">
-        <v>9</v>
-      </c>
-      <c r="N24" t="n">
-        <v>9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>9</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>技术壁垒</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
+      <c r="E36" t="n">
         <v>6</v>
       </c>
-      <c r="D25" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" t="n">
-        <v>7</v>
-      </c>
-      <c r="F25" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>7</v>
-      </c>
-      <c r="I25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>6</v>
-      </c>
-      <c r="K25" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" t="n">
-        <v>4</v>
-      </c>
-      <c r="M25" t="n">
-        <v>7</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>6</v>
-      </c>
-      <c r="P25" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>商业化</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" t="n">
-        <v>6</v>
-      </c>
-      <c r="G26" t="n">
-        <v>5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>7</v>
-      </c>
-      <c r="K26" t="n">
-        <v>7</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6</v>
-      </c>
-      <c r="M26" t="n">
-        <v>8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>7</v>
-      </c>
-      <c r="O26" t="n">
-        <v>9</v>
-      </c>
-      <c r="P26" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="F36" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2756,81 +2387,63 @@
   </sheetPr>
   <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI大模型能力对比</t>
+          <t>AI大模型对比</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>模型</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>厂商</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>推理</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>编程</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>多模态</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>价格竞争力</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>上下文</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>生态</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>输入价格</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr">
         <is>
           <t>输出价格</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>单位</t>
         </is>
       </c>
     </row>
@@ -2845,34 +2458,29 @@
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" s="5" t="n">
+      <c r="G4" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="4" t="n">
         <v>60</v>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>$/1M tokens</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -2886,34 +2494,29 @@
           <t>DeepSeek（幻方量化）</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" s="5" t="n">
+      <c r="G5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="4" t="n">
         <v>8</v>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>$/1M tokens</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -2927,34 +2530,29 @@
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="4" t="n">
         <v>75</v>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>$/1M tokens</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -2968,34 +2566,29 @@
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="4" t="n">
         <v>15</v>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>$/1M tokens</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -3009,34 +2602,29 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="5" t="n">
+      <c r="D8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="5" t="n">
+      <c r="F8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>$/1M tokens</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -3050,34 +2638,29 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="5" t="n">
+      <c r="D9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="4" t="n">
         <v>40</v>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>$/1M tokens</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -3091,34 +2674,29 @@
           <t>字节跳动</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" s="5" t="n">
+      <c r="C10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="5" t="n">
+      <c r="G10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>$/1M tokens</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -3132,34 +2710,29 @@
           <t>阿里巴巴</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="C11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I11" s="5" t="n">
+      <c r="I11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J11" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>$/1M tokens</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -3173,34 +2746,29 @@
           <t>MiniMax</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="C12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I12" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J12" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>$/1M tokens</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -3290,14 +2858,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3307,126 +2869,126 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>月份</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>上证综指</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>纳斯达克</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>恒生科技</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>3350</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>19800</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>5200</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>3420</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>20100</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>5380</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="n">
         <v>3380</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>20500</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>3450</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>21200</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>5650</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="n">
         <v>3987</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>23500</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>5100</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="4" t="n">
         <v>4052.18</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>25948.22</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>4735.8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3439,13 +3001,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3455,139 +3012,190 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>指标</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>单位</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>趋势</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026年全球半导体市场规模预测</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
+          <t>全球半导体收入(2026预测)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>13000</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>亿美元</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>增长90%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>同比增长率</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
+          <t>全球AI市场(2026预测)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>3010</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>亿美元</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>增长35.2%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>中国芯片出口额（1-2月）</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
+          <t>中国芯片出口(1-2月)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>433</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>亿美元</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>同比增长72.6%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>中国芯片出口同比增长</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>72.6%</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
+          <t>三星2nm良率</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>突破</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>三星2nm工艺良率</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
+          <t>Arm AI芯片目标</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>亿美元</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>提前达成</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>韩国AI半导体投入</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>亿韩元</t>
+          <t>SpaceX IPO估值</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>17500</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>亿美元</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>历史最大</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>中国半导体IPO排队企业</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>家</t>
+          <t>英伟达市值</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>亿美元</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>企稳</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>中国半导体已IPO企业（2025以来）</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>家</t>
+          <t>SK海力士市值</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>亿美元</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>突破</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3600,745 +3208,975 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>顶会论文收藏</t>
+          <t>顶会论文汇总</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>论文标题</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>会议</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>奖项</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>机构</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>关键指标</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>链接</t>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>核心指标</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>商业潜力</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>arXiv</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>D4RT: Unified, Fast 4D Scene Reconstruction &amp; Tracking</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>CVPR 2026</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>最佳论文</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Google DeepMind, UCL, Oxford</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>速度提升18-300x</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="E4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2512.08924</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>TRELLIS.2: Native and Compact Structured Latents for 3D Generation</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>CVPR 2026</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>最佳学生论文</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>清华大学、微软研究院、中国科学技术大学</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>17秒生成游戏级PBR资产</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="E5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2512.14692</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>NitroGen: An Open Foundation Model for Generalist Gaming Agents</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>CVPR 2026</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>最佳论文荣誉提名</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>40,000小时训练数据，1000+游戏泛化</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2601.02427</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Transformers are Inherently Succinct</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>ICLR 2026</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>杰出论文奖</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>ETH Zurich, MPI-SWS</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>指数级简洁性证明 + EXPSPACE验证不可能性</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="E7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2510.19315</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>LLMs Get Lost In Multi-Turn Conversation</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>ICLR 2026</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>杰出论文奖</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Salesforce AI Research</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>多轮对话性能下降39%，纠正失败率&gt;95%</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2505.06120</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>OPUS: Towards Efficient and Principled Data Selection in Large Language Model Pre-training in Every Iteration</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>ICML 2026</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Oral</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>未公开</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>1/7数据超越全量训练</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="E9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2602.05400</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Do We Need Adam? Surprisingly Strong and Sparse Reinforcement Learning with SGD in LLMs</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>ICML 2026</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Oral</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>未公开</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>0.02%参数更新匹配AdamW</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2602.07729</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Are VLMs Seeing or Just Saying? Uncovering the Illusion of Visual Perception in Multimodal LLMs</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>ICML 2026</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Oral</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>未公开</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>thinking模型视觉幻觉3倍于普通VLM</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="E11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2605.15864</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>PP-OCRv6: From 1.5M to 34.5M Parameters, Surpassing Billion-Scale VLMs</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.13108</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>SENTINEL: Failure-Driven RL for Tool-Using LLM Agents</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr"/>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.12908</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Boltzmann Attention: Learnable Ising Couplings for Cooperative Attention</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.12478</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>HYDRA-X: Native Unified Multimodal Models with Holistic Visual Tokenizers</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.13289</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>The Hidden Power of Scaling Factor in LoRA Optimization</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.12883</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>PP-OCRv6: From 1.5M to 34.5M Parameters, Surpassing Billion-Scale VLMs</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.13108</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>SENTINEL: Failure-Driven Reinforcement Learning for Tool-Using LLM Agents</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.12908</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Boltzmann Attention: Learnable Ising Couplings for Cooperative Attention</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr"/>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.12478</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>HYDRA-X: Native Unified Multimodal Models with Holistic Visual Tokenizers</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr"/>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.13289</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>The Hidden Power of Scaling Factor in LoRA Optimization</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr"/>
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.12883</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>ExpWeaver: LLM Agents Learn from Experience via Latent RAG</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.01041</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>REFLECT: Intervention-Supported Error Attribution for Silent Failures in LLM Agents</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.09071</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>PP-OCRv6: From 1.5M to 34.5M Parameters, Surpassing Billion-Scale VLMs</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr"/>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>百度</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>34.5M参数超越Billion-scale VLM</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="E24" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.13108</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>SENTINEL: Failure-Driven Reinforcement Learning for Tool-Using LLM Agents</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr"/>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>未公开</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>训练效率提升3-5x</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="E25" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.12908</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Boltzmann Attention: Learnable Ising Couplings for Cooperative Attention</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>未公开</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>注意力协同效果提升</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="E26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.12478</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>HYDRA-X: Native Unified Multimodal Models with Holistic Visual Tokenizers</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>未公开</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>统一多模态架构</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="E27" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.13289</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>The Hidden Power of Scaling Factor in LoRA Optimization</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>未公开</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>NLP/CV任务提升1-3pp</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="E28" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.12883</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>ExpWeaver: LLM Agents Learn from Experience via Latent RAG</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>未公开</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Agent经验复用</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="E29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.01041</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>REFLECT: Intervention-Supported Error Attribution for Silent Failures in LLM Agents</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>arXiv 2026</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>未公开</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>错误检测率+40%</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="E30" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.09071</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Gaze Heads: How VLMs Look at What They Describe</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>揭示VLM跨模态对齐新机制</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.14703</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>OmniVideo-100K: A Dataset for Audio-Visual Reasoning through Structured Scripts and Evidence Chains</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>南京大学、中国科学院自动化研究所</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>10万级结构化音视频推理数据集</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.14702</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>RATS! Patches Talk Through Registers: Emergent Parts in Register Attention Transformers</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University, 美国海军研究办公室, Mayo Clinic</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>无监督视觉概念学习新路径</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.14701</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>RepFusion: Leveraging Multimodal Priors for Denoising in Representation Space</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Meta AI, New York University</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>相近推理预算下优于全新去噪网络</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.14700</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>AdaSR: Adaptive Streaming Reasoning with Hierarchical Relative Policy Optimization</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>东方理工高等研究院、上海交通大学、香港理工大学、东南大学、西交利物浦大学</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>流式推理延迟突破</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.14694</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>CORA: Analyzing and Bridging Thinking-Answer Gap in Multimodal RLVR via Consistency-Oriented Reasoning Alignment</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>中国科学院大学、武汉大学、清华大学、天津大学</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>多模态推理基准性能显著提升</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.14691</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Persona-Pruner: Sculpting Lightweight Models for Role-Playing</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>ICML 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Korea University — TAIL Lab</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>角色专属子网络压缩</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.14695</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Instruct-Particulate: Scaling Feed-Forward 3D Object Articulation with Kinematic Control</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>牛津大学、剑桥大学、南洋理工大学</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>3D关节物体生成效率大幅提升</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.14699</t>
         </is>
       </c>
     </row>
@@ -4346,15 +4184,12 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:C30">
+  <conditionalFormatting sqref="B4:B38">
     <cfRule type="cellIs" priority="1" operator="containsText" dxfId="0">
-      <formula>"最佳论文"</formula>
+      <formula>最佳论文</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="containsText" dxfId="1">
-      <formula>"杰出论文"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="containsText" dxfId="2">
-      <formula>"Oral"</formula>
+      <formula>杰出论文</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4367,1205 +4202,937 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>科技新闻动态</t>
+          <t>科技新闻汇总</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>重要程度</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>摘要</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>DeepSeek-V4预览版发布</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>具备世界顶级推理性能，Agent能力大幅提高，聚焦编程能力与超长代码上下文处理</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.deepseek.com/</t>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>证券APP全面AI原生转型</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>股市应用</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>华泰证券推出'AI涨乐'（业内首款AI原生交易APP），国泰君安发布'君弘灵犀'垂类大模型。AI量化交易全年有望达A股总成交额36.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ithome.com/0/928/052.htm</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>证监会：2026年将深化细化高频量化交易监管</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>股市应用</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>证监会主席吴清明确表示将突出公平性原则，深化细化高频量化交易监管</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cls.cn/detail/2305311</t>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>全球半导体与AI市场预测密集发布</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>半导体/AI</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Gartner预计2026年全球半导体收入超1.3万亿美元(+64%)；IDC预测2026年全球AI市场3010亿美元(+35.2%)；中国成熟制程芯片出口前四个月同比+100.1%</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Gartner, IDC, 国际电子商情</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>中国半导体迎IPO潮</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>美国商务部新规封堵AI芯片流向中企海外分支</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>芯片出口管制</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>商务部发布最新出口管制细则，进一步封堵中国企业在海外设立的分支机构获取先进AI芯片的渠道</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>英伟达CEO黄仁勋拒绝出席参议院AI芯片出口听证会</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>AI芯片</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>黄仁勋以日程冲突为由拒绝出席，此前6月8日在首尔称半导体股票暴跌是买入机会</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>苹果WWDC 2026发布Google Gemini驱动的全新Siri AI</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>AI产品</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>苹果Siri全面接入Google Gemini大模型，实现跨App智能操作、上下文理解和多轮对话</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Anthropic秘密提交S-1，估值9650亿美元逼近万亿</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>AI融资/IPO</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Anthropic秘密向SEC提交S-1，最新估值9650亿美元超越OpenAI，计划10月上市</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>费城半导体指数连续大涨，芯片股创一年最佳表现</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>半导体</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>2025年以来已有10家半导体企业成功IPO，另有85家正在排队申报，涵盖全链条</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.21jingji.com/article/20260108/herald/ae6b3053295d5eca7a34a680d716147e.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>国内'百模大战'再升级</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>阿里、字节跳动、腾讯几乎在同一时期密集发布大模型更新，推理成本持续下降</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.cnblogs.com/ycfenxi/p/20027870</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>英伟达股价10连涨</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>股市应用/半导体</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>英伟达股价实现10个交易日连涨，累计涨幅超18%，为2023年后最长连涨纪录</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/world/2026-04-15/doc-inhupkrh4339902.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>雷军：小米自研芯片出货超百万颗</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>经历6月初暴跌后全球芯片股强劲反弹，费城半导体指数连续三日大涨</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>SpaceX史上最大IPO登陆纳斯达克，估值1.75万亿美元</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>IPO</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>SpaceX发行价135美元，募资约750亿美元，为美国有史以来最大规模IPO</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>台积电CoPoS先进封装技术进入量产准备阶段</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>半导体制造</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>新型Chip-on-Panel-on-Substrate封装技术预计下半年为AI芯片客户提供服务</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>华为AI芯片获字节跳动和阿里巴巴批量订单</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>国产芯片</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>华为昇腾系列AI芯片获得头部互联网公司批量订单，标志国产AI芯片规模化落地</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>供应链消息</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>SpaceX史上最大IPO登陆纳斯达克，估值1.77万亿美元</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>IPO</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>SpaceX发行价135美元，首日收盘161.11美元，募资750亿美元，为美国有史以来最大规模IPO</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>新华网</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>苹果WWDC 2026发布Siri AI，全面接入Google Gemini</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>AI产品</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>新一代Siri基于Gemini模型重构，支持自然对话和跨设备任务，但市场反应冷淡，股价跌1.89%</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>国际金融报</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Anthropic秘密提交S-1，估值9650亿美元</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>AI融资/IPO</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Anthropic已向SEC秘密递交S-1，计划10月上市，Q2营收翻倍，估值首次超越OpenAI</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>TechCrunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>英伟达与SK海力士宣布多年期技术合作</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>半导体</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>小米玄戒系列自研芯片累计出货已超百万颗，同时新款小米机器人正式亮相</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.guancha.cn/economy/2026_04_28_815212.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>OpenAI发布GPT-5.5</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>与DeepSeek V4几乎同期登场，全球大模型进入'7大模型混战'格局</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/wm/2026-04-29/doc-inhwcvff1034726.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Figure发布双机协作人形机器人视频</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>两台搭载Helix02系统的人形机器人在卧室场景中连续完成复杂协作任务</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.aibangbots.com/a/8691</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Anthropic发布Claude 4</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>被称为公司历史上最强大的AI模型，Claude Opus 4被评为全球最佳编程模型，Agentic能力显著增强</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.anthropic.com/news/claude-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Google I/O 2026</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>AI</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>发布Gemini 3.5 Flash、视频模型Omni、全天候AI代理Spark及Android XR，全面聚焦Agentic AI</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/stock/t/2026-05-20/doc-inhynvwq2736993.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>雷军预告小米'三项自研大会师'</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>半导体/AI</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>2026年小米最重磅新品将实现自研芯片（玄戒）、自研OS（澎湃OS）、AI大模型三项'大会师'</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>https://finance.sina.com.cn/tech/roll/2026-05-28/doc-inhzmtwq8605304.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>证券APP全面AI原生转型</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>股市应用</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>华泰证券推出'AI涨乐'（业内首款AI原生交易APP），国泰君安发布'君弘灵犀'垂类大模型。AI量化交易全年有望达A股总成交额36.8%</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ithome.com/0/928/052.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>全球半导体与AI市场预测密集发布</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>半导体/AI</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Gartner预计2026年全球半导体收入超1.3万亿美元(+64%)；IDC预测2026年全球AI市场3010亿美元(+35.2%)；中国成熟制程芯片出口前四个月同比+100.1%</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Gartner, IDC, 国际电子商情</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>双方将联手研发下一代AI内存，SK海力士为Vera Rubin开发专用内存，采用CUDA-X加速芯片仿真</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>财联社</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>美国商务部新规封堵AI芯片流向中企海外分支</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>芯片出口管制</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>商务部发布最新出口管制细则，进一步封堵中国企业在海外设立的分支机构获取先进AI芯片的渠道</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>最新出口管制细则进一步封堵中国企业在海外分支机构获取先进AI芯片的渠道</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>Reuters</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>英伟达CEO黄仁勋拒绝出席参议院AI芯片出口听证会</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>黄仁勋拒绝出席参议院AI芯片出口听证会</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>AI芯片</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>黄仁勋以日程冲突为由拒绝出席，此前6月8日在首尔称半导体股票暴跌是买入机会</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>英伟达CEO以日程冲突为由拒绝出席，此前称半导体股票暴跌是买入机会</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>CNBC</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>苹果WWDC 2026发布Google Gemini驱动的全新Siri AI</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>台积电CoPoS先进封装技术进入量产准备阶段</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>半导体制造</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>新型Chip-on-Panel-on-Substrate封装技术预计下半年为AI芯片客户提供服务</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>华为昇腾芯片获字节跳动和阿里巴巴批量订单</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>国产芯片</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>昇腾950PR测试顺利，字节跳动预计2026年采购超400亿元，标志国产AI芯片规模化落地</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>OFweek</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>费城半导体指数连续大涨，芯片股创一年最佳表现</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>经历6月初暴跌后全球芯片股强劲反弹，SK海力士市值突破1万亿美元</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>韩国投入8000亿韩元加速开发国产在线设备AI半导体</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>韩国政府计划通过建立需求企业、无厂半导体公司、代工厂协作体系，投入8000亿韩元推动本土AI芯片商业化</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>亚洲日报</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>国产AI芯片巨头6月15日上会审核</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>半导体/IPO</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>上海证券交易所上市审核委员会定于6月15日召开审议会议，审核国产AI芯片龙头企业IPO申请</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>WSTS预测2026年全球半导体市场增长90%达1.3万亿美元</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>世界半导体贸易统计组织预测2026年全球半导体市场同比增长约90%，AI算力需求是核心驱动力</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>WSTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>AI拉动芯片需求，半导体ETF涨3.35%</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>行业增长预期强劲，芯片ETF（易方达）涨3.35%，产业链各环节景气度提升</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>财闻网</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>深证成指、创业板指等指数6月15日调整样本股</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>股市</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>深圳证券信息有限公司对深证成指、创业板指等指数实施样本股定期调整，反映A股市场结构新变化</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>深圳证券信息有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>蜜雪冰城以极致性价比模式进军纽约市场</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>消费品牌</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>蜜雪冰城将国内低价高质策略复制到纽约，试图用价格杠杆撬动海外市场</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>财经客户端</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>AI半导体板块6月遭遇剧烈抛售，单日市值蒸发约1.4万亿美元</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>2026年6月初AI半导体板块经历大规模回调，费城半导体指数一度暴跌约10%，英伟达博通等龙头大幅下跌，随后迅速反弹</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Reuters, Intellectia.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Arm有望提前达成150亿美元AI芯片年收入目标</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Arm Holdings CEO Rene Haas表示有望提前实现150亿美元AI芯片年收入目标，数据中心级AI芯片将带来巨额收入，股价一度大涨16%</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Bloomberg, CNBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>苹果WWDC 2026发布全新Siri AI独立应用，深度整合Google Gemini</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>AI产品</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>苹果Siri全面接入Google Gemini大模型，实现跨App智能操作、上下文理解和多轮对话</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>TechCrunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Anthropic秘密提交S-1，估值9650亿美元逼近万亿</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>AI融资/IPO</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Anthropic秘密向SEC提交S-1，最新估值9650亿美元超越OpenAI，计划10月上市</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>TechCrunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>费城半导体指数连续大涨，芯片股创一年最佳表现</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>经历6月初暴跌后全球芯片股强劲反弹，费城半导体指数连续三日大涨</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>SpaceX史上最大IPO登陆纳斯达克，估值1.75万亿美元</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>IPO</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>SpaceX发行价135美元，募资约750亿美元，为美国有史以来最大规模IPO</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>台积电CoPoS先进封装技术进入量产准备阶段</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>半导体制造</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>新型Chip-on-Panel-on-Substrate封装技术预计下半年为AI芯片客户提供服务</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>华为AI芯片获字节跳动和阿里巴巴批量订单</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>国产芯片</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>华为昇腾系列AI芯片获得头部互联网公司批量订单，标志国产AI芯片规模化落地</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>供应链消息</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>SpaceX史上最大IPO登陆纳斯达克，估值1.77万亿美元</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>IPO</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>SpaceX发行价135美元，首日收盘161.11美元，募资750亿美元，为美国有史以来最大规模IPO</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>新华网</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>苹果WWDC 2026发布Siri AI，全面接入Google Gemini</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>AI产品</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>新一代Siri基于Gemini模型重构，支持自然对话和跨设备任务，但市场反应冷淡，股价跌1.89%</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>国际金融报</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Anthropic秘密提交S-1，估值9650亿美元</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>AI融资/IPO</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>Anthropic已向SEC秘密递交S-1，计划10月上市，Q2营收翻倍，估值首次超越OpenAI</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>TechCrunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>英伟达与SK海力士宣布多年期技术合作</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>双方将联手研发下一代AI内存，SK海力士为Vera Rubin开发专用内存，采用CUDA-X加速芯片仿真</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>财联社</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>美国商务部新规封堵AI芯片流向中企海外分支</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>芯片出口管制</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>最新出口管制细则进一步封堵中国企业在海外分支机构获取先进AI芯片的渠道</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>黄仁勋拒绝出席参议院AI芯片出口听证会</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>AI芯片</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>英伟达CEO以日程冲突为由拒绝出席，此前称半导体股票暴跌是买入机会</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>台积电CoPoS先进封装技术进入量产准备阶段</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>半导体制造</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>新型Chip-on-Panel-on-Substrate封装技术预计下半年为AI芯片客户提供服务</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>华为昇腾芯片获字节跳动和阿里巴巴批量订单</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>国产芯片</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>昇腾950PR测试顺利，字节跳动预计2026年采购超400亿元，标志国产AI芯片规模化落地</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>OFweek</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>费城半导体指数连续大涨，芯片股创一年最佳表现</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>经历6月初暴跌后全球芯片股强劲反弹，SK海力士市值突破1万亿美元</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>韩国投入8000亿韩元加速开发国产在线设备AI半导体</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>韩国政府计划通过建立需求企业、无厂半导体公司、代工厂协作体系，投入8000亿韩元推动本土AI芯片商业化</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>亚洲日报</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>国产AI芯片巨头6月15日上会审核</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>半导体/IPO</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>上海证券交易所上市审核委员会定于6月15日召开审议会议，审核国产AI芯片龙头企业IPO申请</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>东方财富</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>WSTS预测2026年全球半导体市场增长90%达1.3万亿美元</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>世界半导体贸易统计组织预测2026年全球半导体市场同比增长约90%，AI算力需求是核心驱动力</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>WSTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>AI拉动芯片需求，半导体ETF涨3.35%</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>行业增长预期强劲，芯片ETF（易方达）涨3.35%，产业链各环节景气度提升</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>财闻网</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>深证成指、创业板指等指数6月15日调整样本股</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>股市</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>深圳证券信息有限公司对深证成指、创业板指等指数实施样本股定期调整，反映A股市场结构新变化</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>深圳证券信息有限公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>蜜雪冰城以极致性价比模式进军纽约市场</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>消费品牌</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>蜜雪冰城将国内低价高质策略复制到纽约，试图用价格杠杆撬动海外市场</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>财经客户端</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>苹果推出全新Siri AI独立应用，底层采用Google Gemini 1.2万亿参数大模型，三层智能架构兼顾性能与隐私</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Apple Newsroom, TechCrunch</t>
         </is>
       </c>
     </row>

--- a/favorites.xlsx
+++ b/favorites.xlsx
@@ -187,12 +187,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$A$2:$A$9</f>
+              <f>'消费品牌AI'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$D$2:$D$9</f>
+              <f>'消费品牌AI'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -219,12 +219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$A$2:$A$9</f>
+              <f>'消费品牌AI'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$E$2:$E$9</f>
+              <f>'消费品牌AI'!$E$2:$E$12</f>
             </numRef>
           </val>
         </ser>
@@ -251,12 +251,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$A$2:$A$9</f>
+              <f>'消费品牌AI'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$F$2:$F$9</f>
+              <f>'消费品牌AI'!$F$2:$F$12</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$A$2:$A$9</f>
+              <f>'消费品牌AI'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$G$2:$G$9</f>
+              <f>'消费品牌AI'!$G$2:$G$12</f>
             </numRef>
           </val>
         </ser>
@@ -315,12 +315,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$A$2:$A$9</f>
+              <f>'消费品牌AI'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$H$2:$H$9</f>
+              <f>'消费品牌AI'!$H$2:$H$12</f>
             </numRef>
           </val>
         </ser>
@@ -528,12 +528,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'股市趋势'!$A$2:$A$11</f>
+              <f>'股市趋势'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'股市趋势'!$B$2:$B$11</f>
+              <f>'股市趋势'!$B$2:$B$12</f>
             </numRef>
           </val>
         </ser>
@@ -560,12 +560,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'股市趋势'!$A$2:$A$11</f>
+              <f>'股市趋势'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'股市趋势'!$C$2:$C$11</f>
+              <f>'股市趋势'!$C$2:$C$12</f>
             </numRef>
           </val>
         </ser>
@@ -592,12 +592,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'股市趋势'!$A$2:$A$11</f>
+              <f>'股市趋势'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'股市趋势'!$D$2:$D$11</f>
+              <f>'股市趋势'!$D$2:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1221,7 +1221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,6 +1872,70 @@
       </c>
       <c r="H20" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>霸王茶姬</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>北美首店开业+冰淇淋品类扩展</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>全球化+品类扩张</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>蜜雪冰城</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>冰淇淋赛道正面竞争霸王茶姬</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>品类竞争</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2337,7 +2401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2510,10 +2574,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4200.5</v>
+        <v>4106.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>23535.7</v>
       </c>
       <c r="D11" t="n">
         <v>4460</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4120</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4520</v>
       </c>
     </row>
   </sheetData>
@@ -2551,22 +2631,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>费城半导体指数连续大涨，芯片股创一年最佳表现</t>
+          <t>WSTS预测2026年全球半导体市场增长90%达1.3万亿美元</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>韩国投入8000亿韩元加速开发国产在线设备AI半导体</t>
+          <t>AI拉动芯片需求，半导体ETF涨3.35%</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2575,13 +2655,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>国产AI芯片巨头6月15日上会审核</t>
+          <t>AI半导体板块6月遭遇剧烈抛售，单日市值蒸发约1.4万亿美元</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2596,7 +2676,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WSTS预测2026年全球半导体市场增长90%达1.3万亿美元</t>
+          <t>Arm有望提前达成150亿美元AI芯片年收入目标</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2611,27 +2691,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI拉动芯片需求，半导体ETF涨3.35%</t>
+          <t>全球半导体股单日蒸发1.3万亿美元创历史最大跌幅</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI半导体板块6月遭遇剧烈抛售，单日市值蒸发约1.4万亿美元</t>
+          <t>英特尔18A制程至强6+处理器发布，单线程领先AMD 30%</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2641,12 +2721,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arm有望提前达成150亿美元AI芯片年收入目标</t>
+          <t>台积电全力扩产AI芯片，释放涨价信号</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2656,42 +2736,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>全球半导体股单日蒸发1.3万亿美元创历史最大跌幅</t>
+          <t>AI芯片需求推动韩国6月上旬出口强劲增长</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>英特尔18A制程至强6+处理器发布，单线程领先AMD 30%</t>
+          <t>AI需求外溢至制造环节，半导体设备ETF涨近3%</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>台积电全力扩产AI芯片，释放涨价信号</t>
+          <t>AI飞轮驱动加速半导体更多领域进入上行周期</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2701,12 +2781,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI芯片需求推动韩国6月上旬出口强劲增长</t>
+          <t>新洁能涨停：功率半导体+产品升级+AI需求增长</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2716,27 +2796,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI需求外溢至制造环节，半导体设备ETF涨近3%</t>
+          <t>英伟达日线11连涨，AI算力龙头再创新高</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI飞轮驱动加速半导体更多领域进入上行周期</t>
+          <t>美股芯片股重挫：纳指跌超2%，费城半导体指数暴跌近8%</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2746,12 +2826,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>新洁能涨停：功率半导体+产品升级+AI需求增长</t>
+          <t>科创芯片设计ETF富国正在发行，2026是AI产业推理落地大年</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2761,12 +2841,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>英伟达日线11连涨，AI算力龙头再创新高</t>
+          <t>港股半导体板块强势：华虹宏力飙升16%，中芯国际涨逾8%</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2785,7 +2865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4087,6 +4167,206 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2606.23668</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>OpenThoughts-Agent: Data Recipes for Agentic Models</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Negin Raoof, Richard Zhuang, Marianna Nezhurina 等</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.24855</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>World Models in Pieces: Structural Certification for General Agents</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Yikai Lu, Yifei Wu, Xinyu Lu, Tongxin Li</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.24842</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Can Scale Save Us From Plasticity Loss in Large Language Models?</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>J. Fernando Hernandez-Garcia, Tomás Figliolia, Beren Millidge</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.24752</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Grading the Grader: Lessons from Evaluating an Agentic Data Analysis System</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Zheng, Hsu</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.24839</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Accuracy and Satisfaction in Multi-Turn LLM Dialogues for NFR Assessment</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fatideh, Baldwin, Dhakal, McMillan, Ghanavati</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.24834</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BluTrain: A C++/CUDA Framework for AI Systems</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Charan, Suresh, Kumar 等</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.24780</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Matching Tasks to Objectives: Fine-Tuning and Prompt-Tuning Strategies for Encoder-Decoder PLMs</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Pouramini, Faili</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.24841</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Solving Inverse Problems of Chaotic Systems with Bidirectional Conditional Flow Matching</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>arXiv 2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hu, Zhang, Pan, Feng, Zhang, Ma, Ting, Li, Wu</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.24824</t>
         </is>
       </c>
     </row>
@@ -4150,17 +4430,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>台积电CoPoS先进封装技术进入量产准备阶段</t>
+          <t>AI拉动芯片需求，半导体ETF涨3.35%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>半导体制造</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4170,61 +4450,61 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>新型Chip-on-Panel-on-Substrate封装技术预计下半年为AI芯片客户提供服务</t>
+          <t>行业增长预期强劲，芯片ETF（易方达）涨3.35%，产业链各环节景气度提升</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>华为昇腾芯片获字节跳动和阿里巴巴批量订单</t>
+          <t>深证成指、创业板指等指数6月15日调整样本股</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>国产芯片</t>
+          <t>股市</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>昇腾950PR测试顺利，字节跳动预计2026年采购超400亿元，标志国产AI芯片规模化落地</t>
+          <t>深圳证券信息有限公司对深证成指、创业板指等指数实施样本股定期调整，反映A股市场结构新变化</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>费城半导体指数连续大涨，芯片股创一年最佳表现</t>
+          <t>蜜雪冰城以极致性价比模式进军纽约市场</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>消费品牌</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>经历6月初暴跌后全球芯片股强劲反弹，SK海力士市值突破1万亿美元</t>
+          <t>蜜雪冰城将国内低价高质策略复制到纽约，试图用价格杠杆撬动海外市场</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4516,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>韩国投入8000亿韩元加速开发国产在线设备AI半导体</t>
+          <t>AI半导体板块6月遭遇剧烈抛售，单日市值蒸发约1.4万亿美元</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4251,7 +4531,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>韩国政府计划通过建立需求企业、无厂半导体公司、代工厂协作体系，投入8000亿韩元推动本土AI芯片商业化</t>
+          <t>2026年6月初AI半导体板块经历大规模回调，费城半导体指数一度暴跌约10%，英伟达博通等龙头大幅下跌，随后迅速反弹</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4543,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>国产AI芯片巨头6月15日上会审核</t>
+          <t>Arm有望提前达成150亿美元AI芯片年收入目标</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>半导体/IPO</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4278,7 +4558,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上海证券交易所上市审核委员会定于6月15日召开审议会议，审核国产AI芯片龙头企业IPO申请</t>
+          <t>Arm Holdings CEO Rene Haas表示有望提前实现150亿美元AI芯片年收入目标，数据中心级AI芯片将带来巨额收入，股价一度大涨16%</t>
         </is>
       </c>
     </row>
@@ -4290,12 +4570,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WSTS预测2026年全球半导体市场增长90%达1.3万亿美元</t>
+          <t>苹果WWDC 2026发布全新Siri AI独立应用，深度整合Google Gemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>AI产品</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4305,19 +4585,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>世界半导体贸易统计组织预测2026年全球半导体市场同比增长约90%，AI算力需求是核心驱动力</t>
+          <t>苹果推出全新Siri AI独立应用，底层采用Google Gemini 1.2万亿参数大模型，三层智能架构兼顾性能与隐私</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AI拉动芯片需求，半导体ETF涨3.35%</t>
+          <t>全球半导体股单日蒸发1.3万亿美元创历史最大跌幅</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4327,56 +4607,56 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>行业增长预期强劲，芯片ETF（易方达）涨3.35%，产业链各环节景气度提升</t>
+          <t>S&amp;P 500芯片股票单日蒸发1.3万亿美元，AI投资过热+贸易不确定性+获利回吐</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>深证成指、创业板指等指数6月15日调整样本股</t>
+          <t>英特尔18A制程至强6+处理器发布，单线程领先AMD 30%</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>股市</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>深圳证券信息有限公司对深证成指、创业板指等指数实施样本股定期调整，反映A股市场结构新变化</t>
+          <t>Computex 2026发布，288能效核，股价涨超6%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>蜜雪冰城以极致性价比模式进军纽约市场</t>
+          <t>台积电全力扩产AI芯片，释放涨价信号</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>消费品牌</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4386,24 +4666,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>蜜雪冰城将国内低价高质策略复制到纽约，试图用价格杠杆撬动海外市场</t>
+          <t>AI芯片需求无放缓迹象，英伟达下代芯片台积电独家代工</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AI半导体板块6月遭遇剧烈抛售，单日市值蒸发约1.4万亿美元</t>
+          <t>Anthropic Claude Opus 4.8基准全面超越GPT-5.5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4413,24 +4693,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026年6月初AI半导体板块经历大规模回调，费城半导体指数一度暴跌约10%，英伟达博通等龙头大幅下跌，随后迅速反弹</t>
+          <t>SWE-bench Pro 69.2%，幻觉率35.9%远低于GPT-5.5的86%，定价更低</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Arm有望提前达成150亿美元AI芯片年收入目标</t>
+          <t>Anthropic完成9650亿美元估值融资，年收入飙至300亿美元</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>AI融资</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4440,24 +4720,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arm Holdings CEO Rene Haas表示有望提前实现150亿美元AI芯片年收入目标，数据中心级AI芯片将带来巨额收入，股价一度大涨16%</t>
+          <t>Series G以9650亿估值完成，年收入从90亿飙至超300亿</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>苹果WWDC 2026发布全新Siri AI独立应用，深度整合Google Gemini</t>
+          <t>谷歌Gemini 3.5 Pro即将发布，200万Token上下文+Deep Think</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AI产品</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4467,7 +4747,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>苹果推出全新Siri AI独立应用，底层采用Google Gemini 1.2万亿参数大模型，三层智能架构兼顾性能与隐私</t>
+          <t>Flash已发布(速度GPT-5.5的4倍且免费)，Pro支持200万Token和深度推理</t>
         </is>
       </c>
     </row>
@@ -4479,39 +4759,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>全球半导体股单日蒸发1.3万亿美元创历史最大跌幅</t>
+          <t>OpenAI转向企业市场，苹果谷歌争夺消费级AI入口</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>S&amp;P 500芯片股票单日蒸发1.3万亿美元，AI投资过热+贸易不确定性+获利回吐</t>
+          <t>AI行业战略分化，OpenAI走企业路线，苹果谷歌走消费路线</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>英特尔18A制程至强6+处理器发布，单线程领先AMD 30%</t>
+          <t>科创板第五套标准扩围至AI大模型企业</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>政策/AI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4521,24 +4801,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Computex 2026发布，288能效核，股价涨超6%</t>
+          <t>上交所发布指引，人工智能大模型企业可适用科创板第五套上市标准，优先支持尚未形成收入规模但具备核心技术的主体，智谱、MiniMax等筹备回A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台积电全力扩产AI芯片，释放涨价信号</t>
+          <t>智谱股价大涨超40%，市值突破万亿港元</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>AI融资</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4548,24 +4828,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI芯片需求无放缓迹象，英伟达下代芯片台积电独家代工</t>
+          <t>智谱股价大涨逾40%，盘中触及2980港元，总市值突破1万亿港元。GLM-5.2模型表现优异，API调用量增幅达400%，公司推进科创板IPO拟募资150亿元</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Anthropic Claude Opus 4.8基准全面超越GPT-5.5</t>
+          <t>MiniMax涨超20%，港股AI大模型双子星闪耀</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AI融资</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4575,105 +4855,105 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SWE-bench Pro 69.2%，幻觉率35.9%远低于GPT-5.5的86%，定价更低</t>
+          <t>MiniMax-W股价攀升20.2%，估值达1876亿港元。作为恒生科技指数新成分股，MiniMax与智谱共同带动港股大模型概念股逆势走强</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Anthropic完成9650亿美元估值融资，年收入飙至300亿美元</t>
+          <t>AI芯片需求推动韩国6月上旬出口强劲增长</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AI融资</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Series G以9650亿估值完成，年收入从90亿飙至超300亿</t>
+          <t>韩国6月前10天出口受AI芯片需求拉动再度强劲增长，半导体出口保持双位数增速，SK海力士市值此前已突破1万亿美元</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>谷歌Gemini 3.5 Pro即将发布，200万Token上下文+Deep Think</t>
+          <t>AI需求外溢至制造环节，半导体设备ETF涨近3%</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Flash已发布(速度GPT-5.5的4倍且免费)，Pro支持200万Token和深度推理</t>
+          <t>AI算力需求向晶圆制造、封装测试等设备环节传导，半导体设备ETF（易方达）涨2.94%，市场关注国产半导体设备厂商替代机会</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OpenAI转向企业市场，苹果谷歌争夺消费级AI入口</t>
+          <t>AI飞轮驱动加速半导体更多领域进入上行周期</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI行业战略分化，OpenAI走企业路线，苹果谷歌走消费路线</t>
+          <t>证券时报报道，AI算力需求持续拉动存储、功率、封装等多环节景气，业内预计2026年全球半导体规模将超1.5万亿美元，内存市场缺口约5%，设备端高景气预见到8个季度后。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>科创板第五套标准扩围至AI大模型企业</t>
+          <t>AI算力新变局：谁能动英伟达奶酪</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>政策/AI</t>
+          <t>AI算力</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4683,51 +4963,51 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>上交所发布指引，人工智能大模型企业可适用科创板第五套上市标准，优先支持尚未形成收入规模但具备核心技术的主体，智谱、MiniMax等筹备回A</t>
+          <t>21财经深度分析，华为昇腾、英特尔18A、AMD、台积电等多方挑战英伟达GPU垄断地位，AI算力格局正从'一家独大'走向多元竞争。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>智谱股价大涨超40%，市值突破万亿港元</t>
+          <t>新洁能涨停：功率半导体+产品升级+AI需求增长</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AI融资</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>智谱股价大涨逾40%，盘中触及2980港元，总市值突破1万亿港元。GLM-5.2模型表现优异，API调用量增幅达400%，公司推进科创板IPO拟募资150亿元</t>
+          <t>A股功率半导体龙头新洁能6月23日涨停，分析师认为AI数据中心功率器件需求+产品升级双轮驱动，功率半导体景气度进入新一轮上行期。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MiniMax涨超20%，港股AI大模型双子星闪耀</t>
+          <t>标普500历史首次站上7000点，纳指涨1.59%至24016点</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AI融资</t>
+          <t>美股</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4737,19 +5017,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MiniMax-W股价攀升20.2%，估值达1876亿港元。作为恒生科技指数新成分股，MiniMax与智谱共同带动港股大模型概念股逆势走强</t>
+          <t>标普500历史首次收盘站上7000点整数关口，纳指涨1.59%至24016.02点，道指微涨220点创历史新高。英伟达日线11连涨，光纤概念股Lumen与AWS合作后暴涨10.13%。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AI芯片需求推动韩国6月上旬出口强劲增长</t>
+          <t>英伟达日线11连涨，AI算力龙头再创新高</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4759,29 +5039,29 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>韩国6月前10天出口受AI芯片需求拉动再度强劲增长，半导体出口保持双位数增速，SK海力士市值此前已突破1万亿美元</t>
+          <t>英伟达股价实现日线11连涨，创2023年以来最长连涨纪录。市场对其数据中心AI GPU需求持续乐观，Vera Rubin平台预期进一步提振估值。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AI需求外溢至制造环节，半导体设备ETF涨近3%</t>
+          <t>港股午盘走低：恒指跌1.13%，科技指数重挫2.21%</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>港股</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4791,19 +5071,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI算力需求向晶圆制造、封装测试等设备环节传导，半导体设备ETF（易方达）涨2.94%，市场关注国产半导体设备厂商替代机会</t>
+          <t>港股恒生指数午盘跌1.13%，恒生科技指数跌2.21%，京东、小米、腾讯、阿里、美团等科技龙头普跌，大模型概念股走低，智谱盘中一度跌超15%。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AI飞轮驱动加速半导体更多领域进入上行周期</t>
+          <t>美股芯片股重挫：纳指跌超2%，费城半导体指数暴跌近8%</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4818,24 +5098,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>证券时报报道，AI算力需求持续拉动存储、功率、封装等多环节景气，业内预计2026年全球半导体规模将超1.5万亿美元，内存市场缺口约5%，设备端高景气预见到8个季度后。</t>
+          <t>美股三大指数集体收跌，纳指重挫2.2%，费城半导体指数暴跌近8%。英伟达跌超4%，美光科技暴跌13%。投资者重新审视AI资本支出规模，质疑大规模芯片投资是否合理。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AI算力新变局：谁能动英伟达奶酪</t>
+          <t>AI投资热潮遭重新审视，资本支出合理性受质疑</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AI算力</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4845,73 +5125,73 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>21财经深度分析，华为昇腾、英特尔18A、AMD、台积电等多方挑战英伟达GPU垄断地位，AI算力格局正从'一家独大'走向多元竞争。</t>
+          <t>分析师开始质疑科技巨头大规模AI资本支出是否合理，市场从追逐AI动量交易转向理性评估。SpaceX暴跌16%加剧科技股恐慌情绪。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>新洁能涨停：功率半导体+产品升级+AI需求增长</t>
+          <t>人工智能让网络安全成为2026年稀缺性投资赛道</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>AI安全</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>A股功率半导体龙头新洁能6月23日涨停，分析师认为AI数据中心功率器件需求+产品升级双轮驱动，功率半导体景气度进入新一轮上行期。</t>
+          <t>AI技术显著降低漏洞挖掘难度，网络安全成为稀缺资产。CrowdStrike八次创盘中新高，帕洛阿尔托网络涨幅228%，ETF收益27%。资金从芯片领域转向安全赛道。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>标普500历史首次站上7000点，纳指涨1.59%至24016点</t>
+          <t>科创芯片设计ETF富国正在发行，2026是AI产业推理落地大年</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>美股</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>标普500历史首次收盘站上7000点整数关口，纳指涨1.59%至24016.02点，道指微涨220点创历史新高。英伟达日线11连涨，光纤概念股Lumen与AWS合作后暴涨10.13%。</t>
+          <t>全球算力资本开支持续攀升，芯片自主可控战略持续加码。科创芯片设计指数成分股2025年净利润同比增速超190%，2026年被视为AI产业推理落地大年。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>英伟达日线11连涨，AI算力龙头再创新高</t>
+          <t>港股半导体板块强势：华虹宏力飙升16%，中芯国际涨逾8%</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4926,24 +5206,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>英伟达股价实现日线11连涨，创2023年以来最长连涨纪录。市场对其数据中心AI GPU需求持续乐观，Vera Rubin平台预期进一步提振估值。</t>
+          <t>港股半导体板块表现强势，华虹宏力飙升16%，中芯国际涨逾8%。恒生科技指数涨1.34%，与美股芯片股暴跌形成鲜明反差，反映资金在港股寻找半导体结构性机会。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>港股午盘走低：恒指跌1.13%，科技指数重挫2.21%</t>
+          <t>A股券商板块延续涨势，28只成分股飘红</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>港股</t>
+          <t>股市</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4953,7 +5233,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>港股恒生指数午盘跌1.13%，恒生科技指数跌2.21%，京东、小米、腾讯、阿里、美团等科技龙头普跌，大模型概念股走低，智谱盘中一度跌超15%。</t>
+          <t>A股市场整体调整后券商板块逆势走强，28只成分股飘红。学者评价'本轮券商上涨的持续性相对更强'，成交额维持在3.46万亿元高位。</t>
         </is>
       </c>
     </row>

--- a/favorites.xlsx
+++ b/favorites.xlsx
@@ -867,12 +867,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'AI大模型'!$A$4:$A$14</f>
+              <f>'AI大模型'!$A$4:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'AI大模型'!$I$4:$I$14</f>
+              <f>'AI大模型'!$I$4:$I$20</f>
             </numRef>
           </val>
         </ser>
@@ -894,12 +894,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'AI大模型'!$A$4:$A$14</f>
+              <f>'AI大模型'!$A$4:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'AI大模型'!$J$4:$J$14</f>
+              <f>'AI大模型'!$J$4:$J$20</f>
             </numRef>
           </val>
         </ser>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -3685,7 +3685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3831,26 +3831,26 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Gemini 3.5 Flash</t>
+          <t>Llama 4</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
         <v>9</v>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3890,26 +3890,26 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Claude 4 Opus</t>
+          <t>DeepSeek V4 (Official)</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>9</v>
       </c>
       <c r="N5" t="n">
+        <v>9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="n">
         <v>10</v>
       </c>
-      <c r="O5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P5" t="n">
-        <v>4</v>
-      </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -3949,26 +3949,26 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Claude 4 Sonnet</t>
+          <t>Gemini 2.5</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" t="n">
         <v>9</v>
       </c>
-      <c r="O6" t="n">
-        <v>8</v>
-      </c>
-      <c r="P6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8</v>
-      </c>
       <c r="R6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -4008,26 +4008,26 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>豆包 2.0</t>
+          <t>Gemini 3.5 Flash</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
         <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -4067,26 +4067,26 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GPT-5.5</t>
+          <t>Qwen3</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
         <v>8</v>
       </c>
       <c r="O8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -4126,26 +4126,26 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DeepSeek V4</t>
+          <t>GPT-5</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
         <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>7</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -4329,33 +4329,249 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>GPT-5</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Claude 4 (2025 Release)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Gemini 2.5</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Llama 4</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 (Official)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>平均</t>
         </is>
       </c>
-      <c r="C15" s="8">
-        <f>AVERAGE(C4:C14)</f>
+      <c r="C21" s="8">
+        <f>AVERAGE(C4:C20)</f>
         <v/>
       </c>
-      <c r="D15" s="8">
-        <f>AVERAGE(D4:D14)</f>
+      <c r="D21" s="8">
+        <f>AVERAGE(D4:D20)</f>
         <v/>
       </c>
-      <c r="E15" s="8">
-        <f>AVERAGE(E4:E14)</f>
+      <c r="E21" s="8">
+        <f>AVERAGE(E4:E20)</f>
         <v/>
       </c>
-      <c r="F15" s="8">
-        <f>AVERAGE(F4:F14)</f>
+      <c r="F21" s="8">
+        <f>AVERAGE(F4:F20)</f>
         <v/>
       </c>
-      <c r="G15" s="8">
-        <f>AVERAGE(G4:G14)</f>
+      <c r="G21" s="8">
+        <f>AVERAGE(G4:G20)</f>
         <v/>
       </c>
-      <c r="H15" s="8">
-        <f>AVERAGE(H4:H14)</f>
+      <c r="H21" s="8">
+        <f>AVERAGE(H4:H20)</f>
         <v/>
       </c>
     </row>
@@ -4363,7 +4579,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:C14">
+  <conditionalFormatting sqref="C4:C20">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4375,7 +4591,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D14">
+  <conditionalFormatting sqref="D4:D20">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4387,7 +4603,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E14">
+  <conditionalFormatting sqref="E4:E20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4399,7 +4615,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F14">
+  <conditionalFormatting sqref="F4:F20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4411,7 +4627,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G14">
+  <conditionalFormatting sqref="G4:G20">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4423,7 +4639,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H14">
+  <conditionalFormatting sqref="H4:H20">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/favorites.xlsx
+++ b/favorites.xlsx
@@ -86,20 +86,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -108,7 +111,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F0C040"/>
+          <fgColor rgb="00FFD700"/>
         </patternFill>
       </fill>
     </dxf>
@@ -238,6 +241,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="3498DB"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
@@ -316,7 +322,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!D3</f>
+              <f>'消费品牌AI'!B19</f>
             </strRef>
           </tx>
           <spPr>
@@ -340,12 +346,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$D$3:$H$3</f>
+              <f>'消费品牌AI'!$B$19:$F$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$D$4:$D$9</f>
+              <f>'消费品牌AI'!$B$20:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -354,7 +360,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!E3</f>
+              <f>'消费品牌AI'!C19</f>
             </strRef>
           </tx>
           <spPr>
@@ -378,12 +384,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$D$3:$H$3</f>
+              <f>'消费品牌AI'!$B$19:$F$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$E$4:$E$9</f>
+              <f>'消费品牌AI'!$C$20:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -392,7 +398,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!F3</f>
+              <f>'消费品牌AI'!D19</f>
             </strRef>
           </tx>
           <spPr>
@@ -416,12 +422,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$D$3:$H$3</f>
+              <f>'消费品牌AI'!$B$19:$F$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$F$4:$F$9</f>
+              <f>'消费品牌AI'!$D$20:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -430,7 +436,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!G3</f>
+              <f>'消费品牌AI'!E19</f>
             </strRef>
           </tx>
           <spPr>
@@ -454,12 +460,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$D$3:$H$3</f>
+              <f>'消费品牌AI'!$B$19:$F$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$G$4:$G$9</f>
+              <f>'消费品牌AI'!$E$20:$E$25</f>
             </numRef>
           </val>
         </ser>
@@ -468,7 +474,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'消费品牌AI'!H3</f>
+              <f>'消费品牌AI'!F19</f>
             </strRef>
           </tx>
           <spPr>
@@ -492,12 +498,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'消费品牌AI'!$D$3:$H$3</f>
+              <f>'消费品牌AI'!$B$19:$F$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'消费品牌AI'!$H$4:$H$9</f>
+              <f>'消费品牌AI'!$F$20:$F$25</f>
             </numRef>
           </val>
         </ser>
@@ -550,7 +556,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>AI大模型能力雷达（Top6）</a:t>
+              <a:t>大模型能力雷达(前6)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -800,7 +806,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>API 价格对比（$/1M tokens）</a:t>
+              <a:t>API价格($/1M tokens)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -907,7 +913,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>三大股指月度趋势</a:t>
+              <a:t>三大股指趋势</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -934,11 +940,8 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="7"/>
+            <size val="6"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="E74C3C"/>
-              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -946,12 +949,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'股市趋势'!$A$4:$A$5</f>
+              <f>'股市趋势'!$A$4:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'股市趋势'!$B$4:$B$5</f>
+              <f>'股市趋势'!$B$4:$B$25</f>
             </numRef>
           </val>
         </ser>
@@ -973,11 +976,8 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="7"/>
+            <size val="6"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="3498DB"/>
-              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -985,12 +985,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'股市趋势'!$A$4:$A$5</f>
+              <f>'股市趋势'!$A$4:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'股市趋势'!$C$4:$C$5</f>
+              <f>'股市趋势'!$C$4:$C$25</f>
             </numRef>
           </val>
         </ser>
@@ -1012,11 +1012,8 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="7"/>
+            <size val="6"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="2ECC71"/>
-              </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1024,12 +1021,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'股市趋势'!$A$4:$A$5</f>
+              <f>'股市趋势'!$A$4:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'股市趋势'!$D$4:$D$5</f>
+              <f>'股市趋势'!$D$4:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -1081,7 +1078,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>半导体/股市关键指标（7-17回调）</a:t>
+              <a:t>半导体关键指标</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1100,18 +1097,21 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="E67E22"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'半导体指标'!$A$4:$A$11</f>
+              <f>'半导体指标'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'半导体指标'!$B$4:$B$11</f>
+              <f>'半导体指标'!$B$4:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -1187,7 +1187,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="5400000"/>
+    <ext cx="7920000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1209,12 +1209,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="5040000"/>
+    <ext cx="7200000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1231,12 +1231,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="4320000"/>
+    <ext cx="7200000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1263,7 +1263,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5040000"/>
+    <ext cx="9360000" cy="5040000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1600,7 +1600,7 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -1706,17 +1706,17 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>股市行情</t>
+          <t>股市记录</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="5">
         <f>SUM(B8:B14)</f>
         <v/>
       </c>
@@ -1755,17 +1755,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1783,552 +1776,610 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>工具/动态</t>
+          <t>AI深度</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>用户体验</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>部署规模</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>技术壁垒</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>商业化</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>类别</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>AI深度</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>用户体验</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>部署规模</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>技术壁垒</t>
-        </is>
-      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>商业化</t>
+          <t>来源日期</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>饿了么</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>蜜雪冰城</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>阿里千问 App</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>瑞幸咖啡</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>出海/AI运营</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>蜜雪冰城</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>出海/AI运营</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>奈雪的茶</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>出海/AI运营</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>霸王茶姬</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>出海/AI运营</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>瑞幸咖啡</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>出海/AI平台</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>霸王茶姬</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>出海/智能调饮</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>星巴克</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>千店千面 AI 体验</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>咖啡 / 门店个性化</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
+      <c r="B13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>门店智能运营</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>大模型/履约</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>蜜雪冰城</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="F15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>美团</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>放心外卖 AI 智能巡检</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>外卖平台 / 食品安全</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>瑞幸咖啡</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>AI 开放平台 + Lucky AI 智能体</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>咖啡 / 开放平台</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>霸王茶姬</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>北美扩张 + 智能调饮</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>新茶饮 / 出海</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>饿了么</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>AI 配送调度系统</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>外卖平台 / 物流调度</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>库迪咖啡</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>智慧运营体系增资</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>咖啡 / 智慧运营</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>霸王茶姬</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>全自动茶饮机 + 千人千味推荐引擎</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>新茶饮 / 智能调饮</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>茶百道</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>“茶茶员工”AI 智能服务台</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>新茶饮 / 门店运营</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>美团</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>LongCat 大模型与 AI Agent 生态</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>本地生活 / AI 平台</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>饿了么</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>AI 商家经营工具套件</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>外卖平台 / 商家服务</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>喜茶</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>AI 智能巡检 Agent</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>新茶饮 / 食安管控</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>瑞幸咖啡</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>全球门店突破3万家，AI开放平台+智能调度支撑超大规模运营</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>出海/AI运营</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>9</v>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>供应链/出海</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>平均</t>
+        </is>
+      </c>
+      <c r="B16" s="4">
+        <f>AVERAGE(B4:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="4">
+        <f>AVERAGE(C4:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>AVERAGE(D4:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>AVERAGE(E4:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>AVERAGE(F4:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>雷达源(品牌×维度)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AI深度</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>用户体验</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>部署规模</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>技术壁垒</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>商业化</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>霸王茶姬</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>瑞幸咖啡</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>霸王茶姬</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>星巴克</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>蜜雪冰城</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>低价策略闯入纽约，雪王爱智慧AI支撑全球供应链与选址</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>出海/AI运营</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
+      <c r="B25" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="C25" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="6" t="n">
+      <c r="D25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="F25" t="n">
         <v>9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>奈雪的茶</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>加州首店三天进账65万，海外门店引入AI溯源与本地化运营</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>出海/AI运营</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>霸王茶姬</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>领跑北美新茶饮“淘金热”，智能调饮设备+茶茶圈私域运营</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>出海/AI运营</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>平均</t>
-        </is>
-      </c>
-      <c r="D19">
-        <f>AVERAGE(D4:D18)</f>
-        <v/>
-      </c>
-      <c r="E19">
-        <f>AVERAGE(E4:E18)</f>
-        <v/>
-      </c>
-      <c r="F19">
-        <f>AVERAGE(F4:F18)</f>
-        <v/>
-      </c>
-      <c r="G19">
-        <f>AVERAGE(G4:G18)</f>
-        <v/>
-      </c>
-      <c r="H19">
-        <f>AVERAGE(H4:H18)</f>
-        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D18">
+  <conditionalFormatting sqref="B4:B15">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2340,7 +2391,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E18">
+  <conditionalFormatting sqref="C4:C15">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2352,7 +2403,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F18">
+  <conditionalFormatting sqref="D4:D15">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2364,7 +2415,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G18">
+  <conditionalFormatting sqref="E4:E15">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2376,7 +2427,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H18">
+  <conditionalFormatting sqref="F4:F15">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2402,22 +2453,14 @@
   <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI 大模型能力与 API 价格</t>
+          <t>AI 大模型能力与价格</t>
         </is>
       </c>
     </row>
@@ -2474,614 +2517,614 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GPT-5.5</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="D4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="4" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>DeepSeek V4</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>DeepSeek（幻方量化）</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="C5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Claude 4 Opus</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" s="6" t="n">
+      <c r="G6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="4" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Claude 4 Sonnet</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="6" t="n">
+      <c r="E7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I7" s="6" t="n">
+      <c r="G7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="J7" s="4" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Gemini 3.5 Flash</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="4" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Gemini 3 Deep Think</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="6" t="n">
+      <c r="E9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I9" s="6" t="n">
+      <c r="G9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="4" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>豆包 2.0</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>字节跳动</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" s="6" t="n">
+      <c r="E10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>通义千问 (Qwen)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>阿里巴巴</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" s="6" t="n">
+      <c r="G11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="4" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>MiniMax</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>MiniMax</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H12" s="6" t="n">
+      <c r="G12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>GLM-5.2</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>智谱</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="6" t="n">
+      <c r="C13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H13" s="6" t="n">
+      <c r="G13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="4" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>LongCat-Flash-Thinking-2601</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>美团</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E14" s="6" t="n">
+      <c r="D14" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>GPT-5</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H15" s="6" t="n">
+      <c r="G15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="4" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Claude 4 (2025 Release)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I16" s="6" t="n">
+      <c r="G16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="4" t="n">
         <v>75</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Gemini 2.5</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E17" s="6" t="n">
+      <c r="D17" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Llama 4</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Meta</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E18" s="6" t="n">
+      <c r="C18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H18" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I18" s="6" t="n">
+      <c r="H18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Alibaba</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E19" s="6" t="n">
+      <c r="C19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I19" s="6" t="n">
+      <c r="G19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>DeepSeek V4 (Official)</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>DeepSeek</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3172,26 +3215,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>三大股指月度趋势</t>
+          <t>三大股指趋势(按日期)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>月份</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3213,33 +3253,333 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3913.79</v>
+        <v>3350</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>25873.18</v>
+        <v>19800</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4797.27</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>3420</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>20100</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>5380</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>3380</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>20500</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>3450</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>21200</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>5650</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>3987</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>23500</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>4031.51</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>25888.84</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>4705.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>4052.18</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>25948.22</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>4735.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>4090.48</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>26517.93</v>
+      </c>
+      <c r="D11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>4163.1</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>24016.02</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>4573.71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>4106.1</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>23535.7</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>4460</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>4120</v>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>4120.28</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>25476.64</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>4423.97</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n">
+        <v>25359.45</v>
+      </c>
+      <c r="D16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>25297.62</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>4073.9</v>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n">
+        <v>4393.01</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>4094.4</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>26213.72</v>
+      </c>
+      <c r="D19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n">
+        <v>4470</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n">
+        <v>26121.16</v>
+      </c>
+      <c r="D21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>3990.24</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>26121.16</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>4507.04</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>3913.79</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>25873.18</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>4797.27</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B24" s="4" t="n">
         <v>3782.45</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C24" s="4" t="n">
         <v>25278.1</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D24" s="4" t="n">
         <v>4587.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>3862.4</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>22851.6</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>4681.5</v>
       </c>
     </row>
   </sheetData>
@@ -3257,17 +3597,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>半导体关键指标</t>
+          <t>半导体关键指标(2026-07)</t>
         </is>
       </c>
     </row>
@@ -3286,81 +3625,101 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>KOSPI单日最大跌幅(%)</t>
+          <t>SOX二季度涨幅(%)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>A股7/17成交额(万亿元)</t>
+          <t>SOX年内涨幅(%)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2.65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>全周融资净卖出(亿元)</t>
+          <t>美光合约价环比(%)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>851</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>恒生科技7/17跌幅(%)</t>
+          <t>美光HBM同比(%)</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4.37</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>创业板指7/17跌幅(%)</t>
+          <t>美光股价年内(%)</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>7.15</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>中芯国际7/17跌幅(%)</t>
+          <t>存储单月销售(亿美元)</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>10</v>
+        <v>746</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>智谱7/17跌幅(%)</t>
+          <t>数据中心成本/GW(亿美元)</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>28</v>
+        <v>700</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>纳斯达克7/17跌幅(%)</t>
+          <t>SK/三星HBM份额(%)</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2.3</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SK/三星扩产(十亿美元)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>英伟达年内涨幅(%)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -3378,20 +3737,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>arXiv / 顶会论文</t>
+          <t>前沿论文</t>
         </is>
       </c>
     </row>
@@ -3408,511 +3767,937 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>摘要</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>日期</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Unified Audio Intelligence Without Regressing on Text Intelligence</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>How Much is Left? LLMs Linearly Encode Their Remaining Output Length</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Mila, McGill University</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Weak-to-Strong Generalization via Direct On-Policy Distillation</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Tsinghua University, ByteDance Seed, Peking University</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>CompactionRL: Reinforcement Learning with Context Compaction for Long-Horizon Agents</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>From Fixed to Free Cameras: Calibration-Free View-Robust Vision-Language-Action Model</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Search Beyond What Can Be Taught: Evolving the Knowledge Boundary in Agentic Visual Generation</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>What Does a Discrete Diffusion Model Learn?</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>OptiAgent: End-to-End Optimization Modeling via Multi-Agent Iterative Refinement</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>LLM-as-a-Verifier: A General-Purpose Verification Framework</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>SovereignPA-Bench: Evaluating User-Owned Personal Agents under Evolving Intent, Platform Mediation, and Consent Constraints</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Graph Sparse Sampling: Breaking the Curse of the Horizon in Continuous MDP Planning</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr"/>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>SteelBench: Evaluating Vision-Language Models in Real-World Industrial Environments</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Erasing Without Collateral Damage: Precise Concept Removal in Diffusion Models</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr"/>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>DSpark: Confidence-Scheduled Speculative Decoding with Semi-Autoregressive Generation</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Statistically Undetectable Backdoors in Deep Neural Networks</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>University of Ottawa / Bocconi University / MIT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>ML/Security</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>证明恶意训练者可在深度网络中植入统计上不可检测的后门，触发后生成不变性对抗样本。</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>2607.09532</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Learning More from Less: Reinforcement Learning from Hindsight</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>MIT / Stanford / UC San Diego</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>RL/Robotics</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>将 hindsight relabeling 引入 VLA 模型的 RL 后训练，把失败轨迹转化为可用训练信号，样本效率提升约 5 倍。</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>2607.09042</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Forget Narrowly, Retain Broadly: Unlearning as an Asymmetric Generalization Problem</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Tübingen AI Center, University of Tübingen</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>ML/Unlearning</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>将机器遗忘重新建模为非对称泛化问题，提出评估协议 SUITE 与 JensUn++ 算法。</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>2607.09236</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Scalable Visual Pretraining for Language Intelligence</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Shanghai AI Laboratory / USTC / ZJU / SJTU</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>ML/Vision-Language</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>直接在视觉文档上进行无监督视觉预训练，无需 OCR 或图文配对监督，在多个基准上优于纯文本预训练。</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>2607.09657</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>OpenLongTail: Generative Scaling of Long-Tail Driving Data</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Texas A&amp;M / NVIDIA / UW-Madison / UT Austin / Yale / Adobe / Meta / Delaware / Stanford</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>CV/Autonomous Driving</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>开源生成式数据引擎，将野外长尾驾驶视频转换为视角对齐、时间一致的多视图训练数据。</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>2607.09655</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Hydra++: Real-Time Hierarchical 3D Scene Graph Construction With Object-Level Shape Estimation</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>MIT / NUS</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>CV/3D</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>实时层次化 3D 场景图构建中嵌入类别无关的物体形状估计，提升物体级与场景级重建质量。</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>2607.09455</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Self-Guided Test-Time Training for Long-Context LLMs</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Meta AI / University of Virginia</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>NLP/Long-Context</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>模型自行识别相关证据片段并仅在这些片段上进行测试时训练，在长上下文基准上取得最高约 15% 相对提升。</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>2607.09415</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>WILDTRACE: Benchmarking Natural Evidence Trails in Long-Context Reasoning</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>HKUST / Qwen Team (Alibaba)</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>NLP/Benchmark</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>构建 481 个任务、214 个真实长文档的基准，评测模型整合远距离自然证据的能力。</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>2607.09328</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Agora: Enhancing LLM Agent Reasoning Via Auction-Based Task Allocation</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>University of Birmingham</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>AI/Agent</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>基于拍卖机制的 LLM Agent 推理步骤分配框架，根据修正后能力动态分配子任务。</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>2607.09600</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>KV-PRM: Efficient Process Reward Modeling via KV-Cache Transfer for Multi-Agent Test-Time Scaling</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>UIUC / Imperial College London / CityU HK</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>ML/Efficiency</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>过程奖励模型复用 LLM 推理时的 KV 缓存，复杂度从 O(L²) 降至 O(L)，评分 FLOPs 最高降低 5000 倍。</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>2607.09153</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Self-GC: Self-Governing Context for Long-Horizon LLM Agents</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>arXiv (cs.AI)</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>面向长程任务的 LLM 智能体上下文自治机制，让 Agent 自主管理、压缩与治理上下文，缓解长时序任务中的上下文膨胀与遗忘。</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>2607.00692</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Can Agents Generalize to the Open World? Unveiling the Fragility of Static Training in Tool Use</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>ICML 2026</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>揭示静态训练的工具使用智能体在开放世界中的脆弱性，指出泛化能力不足是当前工具调用 Agent 的核心短板。</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>2607.01084</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Self-Evolving Agents with Anytime-Valid Certificates</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>arXiv (cs.AI)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>在自我进化的同时提供 anytime-valid 统计有效性证书，让智能体的持续改进带有可验证的置信保证。</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>2607.00871</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>AutoMem: Automated Learning of Memory as a Cognitive Skill</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>arXiv (cs.AI)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Agent</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>把“记忆”当作一种可学习的认知技能进行自动化学习，而非静态外挂检索，提升智能体的长期记忆与调用效率。</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>2607.01224</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Revisiting Chain-of-Thought Reasoning under Limited Supervision</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>arXiv (cs.LG)</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>在有限监督下重新审视思维链推理，提出半监督方法降低对高质量 CoT 标注的依赖。</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>2607.01511</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Beyond Next-Token Prediction: An RLVR Proof of Concept for Tool-Use Agents on Atlassian Workflows</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>arXiv (cs.LG)</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>将可验证奖励强化学习（RLVR）应用于 Atlassian 工作流的工具使用智能体，超越下一 token 预测范式。</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>2607.01465</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>The Wiola Architecture for Efficient Small Language Models</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>arXiv (cs.LG)</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Efficiency</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>提出面向高效小语言模型（SLM）的 Wiola 架构，在端侧/低算力场景下兼顾质量与效率。</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>2607.01394</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Hawk: Harnessing Hardware-Aware Knowledge for High-Performance NPU Kernel Generation</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>arXiv (cs.LG)</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Efficiency</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>利用硬件感知知识自动生成高性能 NPU kernel，面向端侧推理加速与国产算力适配。</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>2607.01590</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Off-Context GRPO: Learning to Reason on Hard Problems using Privileged Information</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>arXiv (cs.LG)</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>RL/Reasoning</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>2607.19313</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>ISO: An RLVR-Native Optimization Stack</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>arXiv (cs.LG)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>RL/Systems</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>2607.19331</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Adopting Reinforcement Learning with Verifiable Rewards for Molecular Generation</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>arXiv (cs.LG)</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>RL/Science</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>2607.19044</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>AdaFlash: Adaptive Speculative Decoding via On-Policy Distilled Diffusion Drafters</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>arXiv (cs.LG)</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Efficiency</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>2607.19223</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Where Should Optimizer State Live? Tiered State Allocation for Memory-Efficient MoE Training</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>arXiv (cs.LG)</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Efficiency</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>2607.19058</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>H²SD: Hybrid Hindsight Self-Distillation</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>arXiv (cs.LG)</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>2607.18955</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Toward Auditable Fraud Detection: Combining Graph Features, Model Explanations, and Agentic Case Investigation</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>arXiv (cs.LG)</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Agent/Application</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>2607.19266</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>From Trajectories to Instructions: Language-Conditioned Meta-Reinforcement Learning</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>arXiv (cs.LG)</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>RL/Agent</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>2607.18830</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:B21">
+  <conditionalFormatting sqref="C4:C43">
     <cfRule type="cellIs" priority="1" operator="containsText" dxfId="0">
       <formula>"最佳论文"</formula>
     </cfRule>
@@ -3930,352 +4715,653 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="66" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>近期科技新闻</t>
+          <t>科技新闻(近期)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>重要程度</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>重要程度</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>摘要</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>A 股上半年红盘收官，科创综指上涨近 54%</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/money/gzqh/futuresyspzx/2026-07-01/doc-iniffqcn6454463.shtml</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>芯片股创历史最佳季度表现，AI 需求可持续性受关注</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-07-01/doc-iniffumk6431034.shtml</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2026 慕尼黑上海电子展前瞻：AI 算力驱动半导体革新</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.xfrb.com.cn/article/kj/14173824741069.html</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>预计今年 AI 手机、AI 电脑销量将首次超过非 AI 产品</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/jjxw/2026-07-07/doc-inifxxwz8253381.shtml</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Omdia：中国半导体市场规模将在 2026 年超过 8000 亿美元，存储芯片暴涨 262.9%</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/jjxw/2026-07-07/doc-inifxxwy1485952.shtml</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>华为发布“韬定律”V2 版本论文，先进封装与 EDA 产业链迎催化</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>https://stock.jrj.com.cn/2026/07/07081057717510.shtml</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>展望半导体 2026 三大关键词：存储、AI、国产化</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cls.cn/detail/2245258</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>科技股回暖：纳指涨超 1.3%，半导体指数升近 4%</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.chnfund.com/article/ARe28939cd-a589-c827-9466-3a224a627ed8</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>三星Q2利润暴增约18倍，股价因AI芯片周期担忧大跌</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.stcn.com/article/detail/4001944.html</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>道指史上首次突破53000点，AI硬件链与科技股反弹</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-07-07/doc-inifxhzh1585788.shtml</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>A股失守4000点，成交额单日缩量约5100亿元</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cnstock.com/commonDetail/739730</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>港股收跌，快手暴跌超12%，半导体跌幅居前</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nbd.com.cn/articles/2026-07-07/4459342.html</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Anthropic将Claude Sonnet 5设为默认模型，Claude Code额度临时提升50%</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>https://caifuhao.eastmoney.com/news/20260702115556044280370</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>SK海力士拟于7月10日登陆纳斯达克，或成全球第二大IPO</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>https://finance.sina.com.cn/stock/usstock/c/2026-06-24/doc-inienxzw6291597.shtml</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Meta 自研 AI 芯片 Iris 将于 9 月量产</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Straits Times / TechCrunch</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Meta 自研 AI 芯片 Iris 将于 9 月量产</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>半导体/AI芯片</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>SK 海力士创纪录 280 亿美元纳斯达克 ADR 上市</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>KuCoin Blog</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Meta MTIA 第四代芯片 Iris 将于 2026 年 9 月台积电量产，2026 年 AI 基础设施开支最高 1450 亿美元，目标 2027 年算力翻倍至 14GW。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>SK 海力士创纪录 280 亿美元纳斯达克 ADR 上市</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>半导体/存储</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>7 月初半导体板块暴跌，英特尔股价大跌 21%</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Forbes</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>SK 海力士 2026 年 7 月 10 日以代码 SKHY 登陆纳斯达克，募资约 280.7 亿美元，史上最大 ADR 发行，巩固 HBM3E/HBM4 垄断地位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>7 月初半导体板块暴跌，英特尔股价大跌 21%</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>半导体/市场</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>中国 5 月芯片出口额同比暴增 110.9%</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>BBC 中文</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>受 AI 资本开支增长质疑及加息担忧影响，2026 年 7 月初半导体板块市值蒸发约 1.3 万亿美元，英特尔股价大跌约 21%。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>中国 5 月芯片出口额同比暴增 110.9%</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>半导体/贸易</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>美国担忧 ASML 最先进 EUV 光刻机可能已流入中国</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>TechCrunch / Reuters</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026 世界人工智能大会将于 7 月 17–20 日在上海举行</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>CCTV 产业+</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>韩国股市AI泡沫恐慌：KOSPI单日暴跌近8%，三星、SK海力士遭抛售，引爆全球半导体回调</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>RFI / 新浪财经</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>2026 年 5 月中国集成电路出口额达 355.5 亿美元，同比增 110.9%，主要由存储芯片涨价及外资在华工厂贡献。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>美国担忧 ASML 最先进 EUV 光刻机可能已流入中国</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>半导体/地缘政治</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>A股遭遇“黑色星期五”：7月17日沪指跌3.05%失守3800点创年内新低，创业板指暴跌7.15%</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>新浪财经 / 格隆汇</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>港股AI产业链全线回调：恒生科技指数跌4.37%，智谱跌超28%、中芯国际跌近10%</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>证券时报</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>存储芯片周期争议：HBM/DRAM涨价见顶担忧引发抛售，机构称“成长逻辑未破”</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>雪球 / 财经</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>美国商务部长对 ASML 表示担忧其最尖端 EUV 设备可能已流入中国，ASML CEO 否认出售，凸显出口管制博弈焦点。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2026 世界人工智能大会将于 7 月 17–20 日在上海举行</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>AI/展会</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>xAI 开源编码智能体 grok-build：Apache 2.0 许可、透明化上下文与 MCP 集成</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>AnalyticsVidhya / GitHub</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>WAIC 2026 以“智能伙伴，共创未来”为主题，汇聚 1100 余家全球企业与 3000 余件展品，首次设立 OPC 专区。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>韩国股市AI泡沫恐慌：KOSPI单日暴跌近8%，三星、SK海力士遭抛售，引爆全球半导体回调</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>半导体/股市</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>存储芯片引领半导体创纪录季度，美光成最大赢家</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>matterfact 半导体周报 / The Financial Exchange</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>7月中旬韩国股市因AI/半导体估值泡沫担忧遭遇恐慌性抛售，KOSPI单日跌幅一度逼近8%触发警报，三星电子、SK海力士两大存储龙头领跌。市场担心HBM/DRAM涨价周期见顶，叠加高杠杆资金出清，成为7月17日全球科技股同步回调的导火索。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>A股遭遇“黑色星期五”：7月17日沪指跌3.05%失守3800点创年内新低，创业板指暴跌7.15%</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>股市/半导体</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>全球存储芯片单月销售额达746亿美元创历史新高</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>澎湃新闻 / WSTS</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>受日韩股市剧烈波动与全球半导体板块暴跌冲击，7月17日A股大幅低开低走，上证综指跌3.05%失守3800点创年内新低，深证成指跌5.4%，创业板指跌7.15%，科创50跌超7%。半导体/存储芯片崩盘（长光华芯、兆易创新等多股跌停），沪深两市成交额放量至2.65万亿元。多家机构判断“本质是杠杆出清而非基本面恶化”，全周融资净卖出逾851亿元。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>港股AI产业链全线回调：恒生科技指数跌4.37%，智谱跌超28%、中芯国际跌近10%</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>股市/AI</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>AI数据中心单GW综合成本升至650-750亿美元，台积电史上首次提价</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Telltales / Nomura</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>7月17日港股受AI产业链集体走弱拖累，恒生指数跌1.78%，恒生科技指数跌4.37%，25000点得而复失。AI大模型股大跌（智谱跌超28%、MiniMax跌超15%），存储芯片板块领跌（兆易创新跌超11%、澜起科技跌超8%），半导体（中芯国际跌近10%、华虹宏力跌超11%）与机器人概念（微创机器人-B跌超17%）同步下挫。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>存储芯片周期争议：HBM/DRAM涨价见顶担忧引发抛售，机构称“成长逻辑未破”</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>英伟达沦为年内表现最差主流芯片股，转向主权AI突围</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>The KE Report / Sherwood</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>在7月全球科技股暴跌之后，市场围绕存储芯片（HBM/DRAM）是周期见顶还是成长中继展开激烈争论。看空方认为韩国半导体估值“靠加杠杆炒出的泡沫”，看多方强调AI算力对高带宽存储的结构性需求仍在扩张、库存健康，属于情绪与杠杆驱动的错杀而非基本面反转。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>xAI 开源编码智能体 grok-build：Apache 2.0 许可、透明化上下文与 MCP 集成</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>AI/开源</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>SK海力士/三星握约80% HBM份额，拟投约5900亿美元扩产；光互连成下一瓶颈</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>matterfact 半导体周报</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>xAI 开源了其编码智能体的 CLI 与终端 UI（grok-build），采用 Apache 2.0 许可，完全透明地展示上下文处理、工具执行、插件、技能与 MCP 集成。虽不接受外部贡献，但开发者可研究、编译并本地运行，被业界评为本月最重磅的开源 AI 发布之一，约 9.3K stars。</t>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D14">
+  <conditionalFormatting sqref="C4:C33">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"高"</formula>
     </cfRule>
